--- a/docs/functions_and_arguments.xlsx
+++ b/docs/functions_and_arguments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\proj\ROAD\road\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B34A6FE-5CAF-4A5A-A0EB-51D7FE5BD6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA15A52B-2E2E-43BB-AB84-AA195AA0F365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -312,12 +312,63 @@
     <t>road_get_* functions</t>
   </si>
   <si>
+    <t>Help</t>
+  </si>
+  <si>
+    <t>locality_type</t>
+  </si>
+  <si>
+    <t>cultural_period</t>
+  </si>
+  <si>
+    <t>technocomplex</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>organic_tool_interpretation</t>
+  </si>
+  <si>
+    <t>symbolic_artifact_interpretation</t>
+  </si>
+  <si>
+    <t>miscellaneous_find_material</t>
+  </si>
+  <si>
+    <t>bibtex</t>
+  </si>
+  <si>
+    <t>assemblages</t>
+  </si>
+  <si>
+    <t>localities</t>
+  </si>
+  <si>
+    <t>road_get_lithic_typologies()</t>
+  </si>
+  <si>
+    <t>road_get_lithic_raw_materials()</t>
+  </si>
+  <si>
+    <t>road_get_features()</t>
+  </si>
+  <si>
+    <t>road_get_publications()</t>
+  </si>
+  <si>
+    <t>LOD 2</t>
+  </si>
+  <si>
+    <t>LOD 3</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos"/>
+        <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t>Symbol legend</t>
@@ -326,7 +377,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos"/>
+        <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
@@ -336,7 +387,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="Aptos"/>
+        <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t>•</t>
@@ -345,7 +396,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos"/>
+        <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Exact search type (equals term)
@@ -356,7 +407,7 @@
         <b/>
         <sz val="8"/>
         <color rgb="FF2F75B5"/>
-        <rFont val="Aptos"/>
+        <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t>○</t>
@@ -365,69 +416,18 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos"/>
+        <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Fuzzy search type (contains term)</t>
     </r>
-  </si>
-  <si>
-    <t>Help</t>
-  </si>
-  <si>
-    <t>locality_type</t>
-  </si>
-  <si>
-    <t>cultural_period</t>
-  </si>
-  <si>
-    <t>technocomplex</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>organic_tool_interpretation</t>
-  </si>
-  <si>
-    <t>symbolic_artifact_interpretation</t>
-  </si>
-  <si>
-    <t>miscellaneous_find_material</t>
-  </si>
-  <si>
-    <t>bibtex</t>
-  </si>
-  <si>
-    <t>assemblages</t>
-  </si>
-  <si>
-    <t>localities</t>
-  </si>
-  <si>
-    <t>road_get_lithic_typologies()</t>
-  </si>
-  <si>
-    <t>road_get_lithic_raw_materials()</t>
-  </si>
-  <si>
-    <t>road_get_features()</t>
-  </si>
-  <si>
-    <t>road_get_publications()</t>
-  </si>
-  <si>
-    <t>LOD 2</t>
-  </si>
-  <si>
-    <t>LOD 3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -475,37 +475,62 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Aptos"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF2F75B5"/>
-      <name val="Aptos"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color rgb="FF2F75B5"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color rgb="FF1E3283"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color rgb="FF1E3283"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FF1E3283"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -544,7 +569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -566,55 +591,46 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -624,6 +640,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF1E3283"/>
       <color rgb="FF2F75B5"/>
     </mruColors>
   </colors>
@@ -902,16 +919,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA191576-E575-4853-A1BC-43BBBFBC35B4}">
   <dimension ref="A1:AD17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="3.7265625" customWidth="1"/>
-    <col min="3" max="3" width="33.1796875" customWidth="1"/>
-    <col min="4" max="30" width="3.7265625" customWidth="1"/>
+    <col min="1" max="2" width="3.7109375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" style="13" customWidth="1"/>
+    <col min="4" max="30" width="3.7109375" style="13" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -947,881 +965,881 @@
       <c r="AC1" s="12"/>
       <c r="AD1" s="12"/>
     </row>
-    <row r="2" spans="1:30" ht="159" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" ht="159" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="K2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" s="13" t="s">
+      <c r="Q2" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="R2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="R2" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" s="13" t="s">
+      <c r="T2" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="U2" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="W2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="X2" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB2" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC2" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD2" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="T2" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="V2" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="W2" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="X2" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y2" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z2" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA2" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB2" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC2" s="13" t="s">
+    </row>
+    <row r="3" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="16">
+        <v>1</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="22"/>
+      <c r="AC3" s="22"/>
+      <c r="AD3" s="21"/>
+    </row>
+    <row r="4" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="15"/>
+      <c r="B4" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
+      <c r="Z4" s="21"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="22"/>
+      <c r="AC4" s="22"/>
+      <c r="AD4" s="21"/>
+    </row>
+    <row r="5" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="15"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="AD2" s="13" t="s">
-        <v>85</v>
-      </c>
+      <c r="D5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="21"/>
+      <c r="X5" s="21"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC5" s="22"/>
+      <c r="AD5" s="21"/>
     </row>
-    <row r="3" spans="1:30" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="15">
+    <row r="6" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="15"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="21"/>
+      <c r="N6" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="21"/>
+      <c r="X6" s="21"/>
+      <c r="Y6" s="21"/>
+      <c r="Z6" s="21"/>
+      <c r="AA6" s="21"/>
+      <c r="AB6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="21"/>
+    </row>
+    <row r="7" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="15"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="21"/>
+      <c r="W7" s="21"/>
+      <c r="X7" s="21"/>
+      <c r="Y7" s="21"/>
+      <c r="Z7" s="21"/>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="21"/>
+    </row>
+    <row r="8" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="15"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="21"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="21"/>
+      <c r="AA8" s="21"/>
+      <c r="AB8" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="21"/>
+    </row>
+    <row r="9" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="15"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="21"/>
+      <c r="AA9" s="21"/>
+      <c r="AB9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="21"/>
+    </row>
+    <row r="10" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="15"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="21"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="21"/>
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="21"/>
+      <c r="AB10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="21"/>
+    </row>
+    <row r="11" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="15"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="U11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="V11" s="21"/>
+      <c r="W11" s="21"/>
+      <c r="X11" s="21"/>
+      <c r="Y11" s="21"/>
+      <c r="Z11" s="21"/>
+      <c r="AA11" s="21"/>
+      <c r="AB11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="21"/>
+    </row>
+    <row r="12" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="15"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="W12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC12" s="22"/>
+      <c r="AD12" s="21"/>
+    </row>
+    <row r="13" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="15"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="21"/>
+    </row>
+    <row r="14" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="15"/>
+      <c r="B14" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
-      <c r="T3" s="18"/>
-      <c r="U3" s="18"/>
-      <c r="V3" s="18"/>
-      <c r="W3" s="18"/>
-      <c r="X3" s="18"/>
-      <c r="Y3" s="18"/>
-      <c r="Z3" s="18"/>
-      <c r="AA3" s="18"/>
-      <c r="AB3" s="19"/>
-      <c r="AC3" s="19"/>
-      <c r="AD3" s="18"/>
+      <c r="D14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="22"/>
     </row>
-    <row r="4" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="14"/>
-      <c r="B4" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
-      <c r="V4" s="18"/>
-      <c r="W4" s="18"/>
-      <c r="X4" s="18"/>
-      <c r="Y4" s="18"/>
-      <c r="Z4" s="18"/>
-      <c r="AA4" s="18"/>
-      <c r="AB4" s="19"/>
-      <c r="AC4" s="19"/>
-      <c r="AD4" s="18"/>
+    <row r="15" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="15"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD15" s="21" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="14"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="23"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-      <c r="S5" s="18"/>
-      <c r="T5" s="18"/>
-      <c r="U5" s="18"/>
-      <c r="V5" s="18"/>
-      <c r="W5" s="18"/>
-      <c r="X5" s="18"/>
-      <c r="Y5" s="18"/>
-      <c r="Z5" s="18"/>
-      <c r="AA5" s="18"/>
-      <c r="AB5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC5" s="19"/>
-      <c r="AD5" s="18"/>
+    <row r="16" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
     </row>
-    <row r="6" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="14"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="23"/>
-      <c r="N6" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="18"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="18"/>
-      <c r="AB6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="18"/>
-    </row>
-    <row r="7" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="14"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="18"/>
-      <c r="S7" s="18"/>
-      <c r="T7" s="18"/>
-      <c r="U7" s="18"/>
-      <c r="V7" s="18"/>
-      <c r="W7" s="18"/>
-      <c r="X7" s="18"/>
-      <c r="Y7" s="18"/>
-      <c r="Z7" s="18"/>
-      <c r="AA7" s="18"/>
-      <c r="AB7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC7" s="19"/>
-      <c r="AD7" s="18"/>
-    </row>
-    <row r="8" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="14"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="R8" s="18"/>
-      <c r="S8" s="18"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18"/>
-      <c r="V8" s="18"/>
-      <c r="W8" s="18"/>
-      <c r="X8" s="18"/>
-      <c r="Y8" s="18"/>
-      <c r="Z8" s="18"/>
-      <c r="AA8" s="18"/>
-      <c r="AB8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC8" s="19"/>
-      <c r="AD8" s="18"/>
-    </row>
-    <row r="9" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="14"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="S9" s="18"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="18"/>
-      <c r="V9" s="18"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="18"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="18"/>
-      <c r="AA9" s="18"/>
-      <c r="AB9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="18"/>
-    </row>
-    <row r="10" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="14"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="18"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="18"/>
-      <c r="Y10" s="18"/>
-      <c r="Z10" s="18"/>
-      <c r="AA10" s="18"/>
-      <c r="AB10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC10" s="19"/>
-      <c r="AD10" s="18"/>
-    </row>
-    <row r="11" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="14"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="U11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="V11" s="18"/>
-      <c r="W11" s="18"/>
-      <c r="X11" s="18"/>
-      <c r="Y11" s="18"/>
-      <c r="Z11" s="18"/>
-      <c r="AA11" s="18"/>
-      <c r="AB11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="18"/>
-    </row>
-    <row r="12" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="14"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="W12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="X12" s="18"/>
-      <c r="Y12" s="18"/>
-      <c r="Z12" s="18"/>
-      <c r="AA12" s="18"/>
-      <c r="AB12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC12" s="19"/>
-      <c r="AD12" s="18"/>
-    </row>
-    <row r="13" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="14"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="18"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="18"/>
-      <c r="W13" s="18"/>
-      <c r="X13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="18"/>
-    </row>
-    <row r="14" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="14"/>
-      <c r="B14" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
-      <c r="U14" s="25"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="25"/>
-      <c r="X14" s="25"/>
-      <c r="Y14" s="25"/>
-      <c r="Z14" s="25"/>
-      <c r="AA14" s="25"/>
-      <c r="AB14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC14" s="19"/>
-      <c r="AD14" s="19"/>
-    </row>
-    <row r="15" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="14"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
-      <c r="Y15" s="25"/>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="19"/>
-      <c r="AC15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD15" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="25"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="25"/>
-      <c r="V16" s="25"/>
-      <c r="W16" s="25"/>
-      <c r="X16" s="25"/>
-      <c r="Y16" s="25"/>
-      <c r="Z16" s="25"/>
-      <c r="AA16" s="25"/>
-      <c r="AB16" s="19"/>
-      <c r="AC16" s="19"/>
-      <c r="AD16" s="25"/>
-    </row>
-    <row r="17" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="14"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="16" t="s">
+    <row r="17" spans="1:30" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="15"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="25"/>
-      <c r="X17" s="25"/>
-      <c r="Y17" s="25"/>
-      <c r="Z17" s="25"/>
-      <c r="AA17" s="25"/>
-      <c r="AB17" s="19"/>
-      <c r="AC17" s="19"/>
-      <c r="AD17" s="25"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="22"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1841,56 +1859,56 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DF78EAC-8188-4FCB-BF9A-2F2ECCDC7D75}">
   <dimension ref="A1:BW16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7265625" customWidth="1"/>
-    <col min="2" max="2" width="33.1796875" customWidth="1"/>
-    <col min="3" max="75" width="3.7265625" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="3" max="75" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="8"/>
-      <c r="AH1" s="8"/>
-      <c r="AI1" s="8"/>
-      <c r="AJ1" s="8"/>
-      <c r="AK1" s="8"/>
-      <c r="AL1" s="8"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
       <c r="AM1" s="10"/>
       <c r="AN1" s="10"/>
       <c r="AO1" s="10"/>
@@ -1905,16 +1923,16 @@
       <c r="AX1" s="10"/>
       <c r="AY1" s="10"/>
       <c r="AZ1" s="10"/>
-      <c r="BB1" s="8"/>
-      <c r="BC1" s="8"/>
-      <c r="BD1" s="8"/>
-      <c r="BE1" s="8"/>
-      <c r="BF1" s="8"/>
-      <c r="BG1" s="8"/>
-      <c r="BH1" s="8"/>
-      <c r="BI1" s="8"/>
-      <c r="BJ1" s="8"/>
-      <c r="BK1" s="8"/>
+      <c r="BB1" s="9"/>
+      <c r="BC1" s="9"/>
+      <c r="BD1" s="9"/>
+      <c r="BE1" s="9"/>
+      <c r="BF1" s="9"/>
+      <c r="BG1" s="9"/>
+      <c r="BH1" s="9"/>
+      <c r="BI1" s="9"/>
+      <c r="BJ1" s="9"/>
+      <c r="BK1" s="9"/>
       <c r="BL1" s="10"/>
       <c r="BM1" s="10"/>
       <c r="BN1" s="10"/>
@@ -1928,7 +1946,7 @@
       <c r="BV1" s="10"/>
       <c r="BW1" s="10"/>
     </row>
-    <row r="2" spans="1:75" ht="213" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:75" ht="219" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>41</v>
@@ -2113,8 +2131,8 @@
       <c r="BV2" s="4"/>
       <c r="BW2" s="4"/>
     </row>
-    <row r="3" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2222,8 +2240,8 @@
       <c r="BV3" s="6"/>
       <c r="BW3" s="6"/>
     </row>
-    <row r="4" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A4" s="9"/>
+    <row r="4" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2337,8 +2355,8 @@
       <c r="BV4" s="5"/>
       <c r="BW4" s="5"/>
     </row>
-    <row r="5" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A5" s="9"/>
+    <row r="5" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2458,8 +2476,8 @@
       <c r="BV5" s="5"/>
       <c r="BW5" s="5"/>
     </row>
-    <row r="6" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
+    <row r="6" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
@@ -2579,8 +2597,8 @@
       <c r="BV6" s="5"/>
       <c r="BW6" s="5"/>
     </row>
-    <row r="7" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
+    <row r="7" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2702,8 +2720,8 @@
       <c r="BV7" s="5"/>
       <c r="BW7" s="5"/>
     </row>
-    <row r="8" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A8" s="9"/>
+    <row r="8" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
@@ -2827,8 +2845,8 @@
       <c r="BV8" s="5"/>
       <c r="BW8" s="5"/>
     </row>
-    <row r="9" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A9" s="9"/>
+    <row r="9" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2944,8 +2962,8 @@
       <c r="BV9" s="5"/>
       <c r="BW9" s="5"/>
     </row>
-    <row r="10" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A10" s="9"/>
+    <row r="10" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
@@ -3065,8 +3083,8 @@
       <c r="BV10" s="5"/>
       <c r="BW10" s="5"/>
     </row>
-    <row r="11" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A11" s="9"/>
+    <row r="11" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A11" s="8"/>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
@@ -3192,8 +3210,8 @@
       <c r="BV11" s="5"/>
       <c r="BW11" s="5"/>
     </row>
-    <row r="12" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A12" s="9"/>
+    <row r="12" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A12" s="8"/>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
@@ -3311,8 +3329,8 @@
       <c r="BV12" s="5"/>
       <c r="BW12" s="5"/>
     </row>
-    <row r="13" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A13" s="9"/>
+    <row r="13" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
@@ -3434,8 +3452,8 @@
       <c r="BV13" s="5"/>
       <c r="BW13" s="5"/>
     </row>
-    <row r="14" spans="1:75" x14ac:dyDescent="0.35">
-      <c r="A14" s="9"/>
+    <row r="14" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A14" s="8"/>
       <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
@@ -3541,7 +3559,7 @@
       <c r="BV14" s="5"/>
       <c r="BW14" s="5"/>
     </row>
-    <row r="15" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="1" t="s">
         <v>38</v>
@@ -3620,7 +3638,7 @@
       <c r="BV15" s="2"/>
       <c r="BW15" s="2"/>
     </row>
-    <row r="16" spans="1:75" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="1" t="s">
         <v>39</v>
